--- a/running/聖建様_ランニングコスト明細.xlsx
+++ b/running/聖建様_ランニングコスト明細.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="222">
   <si>
     <t xml:space="preserve">月額ランニングコスト（受講者数別）</t>
   </si>
@@ -238,16 +238,174 @@
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FF1A2430"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">インフラ・</t>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AWS </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">固定費</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EC2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RDS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ElastiCache</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ALB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Route53</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AWS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に直接お支払いいただく分</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">その他</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1A2430"/>
         <rFont val="Meiryo"/>
         <family val="0"/>
         <charset val="1"/>
@@ -266,34 +424,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF6C7A87"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">サーバー、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF6C7A87"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF6C7A87"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、キャッシュ、監視、バックアップ、ドメイン等</t>
-    </r>
+    <t xml:space="preserve">監視サービス（無料枠から開始可）、アバター・音声合成（教材制作中のみ）</t>
   </si>
   <si>
     <t xml:space="preserve">固定費 小計</t>
@@ -715,6 +846,145 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">名あたりの負担は下がります</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFB05A1E"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">うち </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFB05A1E"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AWS</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFB05A1E"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へのお支払い（固定＋変動）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">変動費はすべて</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AWS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CDN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rekognition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6C7A87"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）です</t>
     </r>
   </si>
   <si>
@@ -4279,7 +4549,7 @@
     <numFmt numFmtId="172" formatCode="\¥#,##0.0"/>
     <numFmt numFmtId="173" formatCode="\¥#,##0.00"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4384,6 +4654,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFB05A1E"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF1A2430"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
@@ -4410,6 +4687,13 @@
       <name val="Meiryo"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFB05A1E"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -4656,7 +4940,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4705,6 +4989,18 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4717,31 +5013,43 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4749,15 +5057,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4767,14 +5075,6 @@
     </xf>
     <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -4797,7 +5097,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4809,11 +5109,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4825,7 +5125,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4833,23 +5133,23 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4857,15 +5157,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4873,11 +5173,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4885,19 +5185,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5153,7 +5453,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -5236,302 +5536,342 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="10" t="n">
-        <f aca="false">02_単価と前提!$B$24-02_単価と前提!$B$15</f>
-        <v>24200</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <f aca="false">02_単価と前提!$B$24-02_単価と前提!$B$15</f>
-        <v>24200</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <f aca="false">02_単価と前提!$B$24-02_単価と前提!$B$15</f>
-        <v>24200</v>
-      </c>
-      <c r="E9" s="11" t="s">
+      <c r="B9" s="13" t="n">
+        <f aca="false">SUM(02_単価と前提!$B$16:$B$20)+02_単価と前提!$B$22</f>
+        <v>16200</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <f aca="false">SUM(02_単価と前提!$B$16:$B$20)+02_単価と前提!$B$22</f>
+        <v>16200</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <f aca="false">SUM(02_単価と前提!$B$16:$B$20)+02_単価と前提!$B$22</f>
+        <v>16200</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+    <row r="10" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="13" t="n">
-        <f aca="false">SUM(B8:B9)</f>
+      <c r="B10" s="10" t="n">
+        <f aca="false">02_単価と前提!$B$21+02_単価と前提!$B$23</f>
+        <v>8000</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <f aca="false">02_単価と前提!$B$21+02_単価と前提!$B$23</f>
+        <v>8000</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <f aca="false">02_単価と前提!$B$21+02_単価と前提!$B$23</f>
+        <v>8000</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <f aca="false">SUM(B8:B10)</f>
         <v>104200</v>
       </c>
-      <c r="C10" s="13" t="n">
-        <f aca="false">SUM(C8:C9)</f>
+      <c r="C11" s="16" t="n">
+        <f aca="false">SUM(C8:C10)</f>
         <v>104200</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <f aca="false">SUM(D8:D9)</f>
+      <c r="D11" s="16" t="n">
+        <f aca="false">SUM(D8:D10)</f>
         <v>104200</v>
       </c>
-      <c r="E10" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-    </row>
-    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="10" t="n">
+      <c r="E11" s="17"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="10" t="n">
         <f aca="false">ROUND(MAX(0,$B$5*02_単価と前提!$B$6-02_単価と前提!$B$11)*02_単価と前提!$B$28,0)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C14" s="10" t="n">
         <f aca="false">ROUND(MAX(0,$C$5*02_単価と前提!$B$6-02_単価と前提!$B$11)*02_単価と前提!$B$28,0)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D14" s="10" t="n">
         <f aca="false">ROUND(MAX(0,$D$5*02_単価と前提!$B$6-02_単価と前提!$B$11)*02_単価と前提!$B$28,0)</f>
         <v>445</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="10" t="n">
+      <c r="E14" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="10" t="n">
         <f aca="false">ROUND((50+$B$5*0.02)*02_単価と前提!$B$29,0)</f>
         <v>191</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C15" s="10" t="n">
         <f aca="false">ROUND((50+$C$5*0.02)*02_単価と前提!$B$29,0)</f>
         <v>195</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D15" s="10" t="n">
         <f aca="false">ROUND((50+$D$5*0.02)*02_単価と前提!$B$29,0)</f>
         <v>210</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="10" t="n">
+      <c r="E15" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="10" t="n">
         <f aca="false">ROUND($B$5*02_単価と前提!$B$7*02_単価と前提!$B$30,0)</f>
         <v>165</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C16" s="10" t="n">
         <f aca="false">ROUND($C$5*02_単価と前提!$B$7*02_単価と前提!$B$30,0)</f>
         <v>330</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D16" s="10" t="n">
         <f aca="false">ROUND($D$5*02_単価と前提!$B$7*02_単価と前提!$B$30,0)</f>
         <v>990</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="10" t="n">
+      <c r="E16" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="10" t="n">
         <f aca="false">ROUND($B$5*02_単価と前提!$B$8*02_単価と前提!$B$31,0)</f>
         <v>146</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C17" s="10" t="n">
         <f aca="false">ROUND($C$5*02_単価と前提!$B$8*02_単価と前提!$B$31,0)</f>
         <v>293</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D17" s="10" t="n">
         <f aca="false">ROUND($D$5*02_単価と前提!$B$8*02_単価と前提!$B$31,0)</f>
         <v>878</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="10" t="n">
+      <c r="E17" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="10" t="n">
         <f aca="false">ROUND($B$5*5*02_単価と前提!$B$32,0)</f>
         <v>5</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C18" s="10" t="n">
         <f aca="false">ROUND($C$5*5*02_単価と前提!$B$32,0)</f>
         <v>10</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D18" s="10" t="n">
         <f aca="false">ROUND($D$5*5*02_単価と前提!$B$32,0)</f>
         <v>30</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="13" t="n">
-        <f aca="false">SUM(B13:B17)</f>
+      <c r="E18" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="16" t="n">
+        <f aca="false">SUM(B14:B18)</f>
         <v>507</v>
       </c>
-      <c r="C18" s="13" t="n">
-        <f aca="false">SUM(C13:C17)</f>
+      <c r="C19" s="16" t="n">
+        <f aca="false">SUM(C14:C18)</f>
         <v>828</v>
       </c>
-      <c r="D18" s="13" t="n">
-        <f aca="false">SUM(D13:D17)</f>
+      <c r="D19" s="16" t="n">
+        <f aca="false">SUM(D14:D18)</f>
         <v>2553</v>
       </c>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="17" t="n">
-        <f aca="false">B10+B18</f>
+      <c r="E19" s="17"/>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="20" t="n">
+        <f aca="false">B11+B19</f>
         <v>104707</v>
       </c>
-      <c r="C20" s="17" t="n">
-        <f aca="false">C10+C18</f>
+      <c r="C21" s="20" t="n">
+        <f aca="false">C11+C19</f>
         <v>105028</v>
       </c>
-      <c r="D20" s="17" t="n">
-        <f aca="false">D10+D18</f>
+      <c r="D21" s="20" t="n">
+        <f aca="false">D11+D19</f>
         <v>106753</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="18" t="n">
-        <f aca="false">ROUND(B20/B5,0)</f>
+      <c r="E21" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="21" t="n">
+        <f aca="false">ROUND(B21/B5,0)</f>
         <v>2094</v>
       </c>
-      <c r="C21" s="18" t="n">
-        <f aca="false">ROUND(C20/C5,0)</f>
+      <c r="C22" s="21" t="n">
+        <f aca="false">ROUND(C21/C5,0)</f>
         <v>1050</v>
       </c>
-      <c r="D21" s="18" t="n">
-        <f aca="false">ROUND(D20/D5,0)</f>
+      <c r="D22" s="21" t="n">
+        <f aca="false">ROUND(D21/D5,0)</f>
         <v>356</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-    </row>
-    <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
+      <c r="E22" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="20" t="n">
+    </row>
+    <row r="23" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="23" t="n">
+        <f aca="false">B9+B19</f>
+        <v>16707</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <f aca="false">C9+C19</f>
+        <v>17028</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <f aca="false">D9+D19</f>
+        <v>18753</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="26" t="n">
         <f aca="false">ROUND($B$5*02_単価と前提!$B$9*02_単価と前提!$B$10,0)</f>
         <v>18000</v>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C26" s="26" t="n">
         <f aca="false">ROUND($C$5*02_単価と前提!$B$9*02_単価と前提!$B$10,0)</f>
         <v>36000</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D26" s="26" t="n">
         <f aca="false">ROUND($D$5*02_単価と前提!$B$9*02_単価と前提!$B$10,0)</f>
         <v>108000</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="21" t="n">
+      <c r="E26" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="27" t="n">
         <f aca="false">$B$5*02_単価と前提!$B$9</f>
         <v>500000</v>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C27" s="27" t="n">
         <f aca="false">$C$5*02_単価と前提!$B$9</f>
         <v>1000000</v>
       </c>
-      <c r="D25" s="21" t="n">
+      <c r="D27" s="27" t="n">
         <f aca="false">$D$5*02_単価と前提!$B$9</f>
         <v>3000000</v>
       </c>
-      <c r="E25" s="22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="23" t="n">
-        <f aca="false">B25-B20-B24</f>
+      <c r="E27" s="28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="29" t="n">
+        <f aca="false">B27-B21-B26</f>
         <v>377293</v>
       </c>
-      <c r="C26" s="23" t="n">
-        <f aca="false">C25-C20-C24</f>
+      <c r="C28" s="29" t="n">
+        <f aca="false">C27-C21-C26</f>
         <v>858972</v>
       </c>
-      <c r="D26" s="23" t="n">
-        <f aca="false">D25-D20-D24</f>
+      <c r="D28" s="29" t="n">
+        <f aca="false">D27-D21-D26</f>
         <v>2785247</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="25" t="s">
-        <v>39</v>
+      <c r="E28" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="25" t="s">
-        <v>40</v>
+      <c r="A30" s="30" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="25" t="s">
-        <v>41</v>
+      <c r="A31" s="31" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25" t="s">
-        <v>42</v>
+      <c r="A32" s="31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="31" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -5561,17 +5901,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>45</v>
+      <c r="A4" s="32" t="s">
+        <v>49</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -5580,98 +5920,98 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="B5" s="33" t="n">
         <v>150</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
+      <c r="C5" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="30" t="n">
+      <c r="A6" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="34" t="n">
         <v>3.5</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="31" t="n">
+      <c r="A7" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="35" t="n">
         <v>22</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="31" t="n">
+      <c r="A8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="35" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="B9" s="36" t="n">
         <v>10000</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="33" t="n">
+        <v>60</v>
+      </c>
+      <c r="B10" s="37" t="n">
         <v>0.036</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="34" t="n">
+      <c r="A11" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="38" t="n">
         <v>1024</v>
       </c>
-      <c r="C11" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
+      <c r="C11" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -5683,182 +6023,182 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="32" t="n">
+      <c r="B15" s="36" t="n">
         <v>80000</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="D15" s="40" t="s">
+        <v>70</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="32" t="n">
+      <c r="A16" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="36" t="n">
         <v>4500</v>
       </c>
-      <c r="C16" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>71</v>
+      <c r="C16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="32" t="n">
+      <c r="A17" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="C17" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>70</v>
+      <c r="C17" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>74</v>
       </c>
       <c r="E17" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="36" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="41" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="32" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>77</v>
+      <c r="E18" s="14" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="32" t="n">
+      <c r="A19" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="36" t="n">
         <v>3500</v>
       </c>
-      <c r="C19" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>70</v>
+      <c r="C19" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>74</v>
       </c>
       <c r="E19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="32" t="n">
+      <c r="A20" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="36" t="n">
         <v>200</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>82</v>
+        <v>85</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>86</v>
       </c>
       <c r="E20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="32" t="n">
+      <c r="A21" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="36" t="n">
         <v>3000</v>
       </c>
-      <c r="C21" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>85</v>
+      <c r="C21" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>89</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="32" t="n">
+      <c r="A22" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="36" t="n">
         <v>500</v>
       </c>
-      <c r="C22" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="28" t="s">
+      <c r="C22" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="36" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="40" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="32" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="36" t="s">
-        <v>85</v>
-      </c>
       <c r="E23" s="11" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="13" t="n">
+      <c r="A24" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="16" t="n">
         <f aca="false">SUM(B15:B23)</f>
         <v>104200</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -5870,148 +6210,148 @@
         <v>2</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" s="38" t="n">
+      <c r="A28" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="42" t="n">
         <f aca="false">0.114*$B$5</f>
         <v>17.1</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>98</v>
+      <c r="C28" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>102</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="38" t="n">
+      <c r="A29" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="42" t="n">
         <f aca="false">0.025*$B$5</f>
         <v>3.75</v>
       </c>
-      <c r="C29" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>101</v>
+      <c r="C29" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" s="39" t="n">
+      <c r="A30" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="43" t="n">
         <f aca="false">0.001*$B$5</f>
         <v>0.15</v>
       </c>
-      <c r="C30" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>104</v>
+      <c r="C30" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>108</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="39" t="n">
+      <c r="A31" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="43" t="n">
         <f aca="false">0.0195*$B$5</f>
         <v>2.925</v>
       </c>
-      <c r="C31" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" s="28" t="s">
-        <v>106</v>
+      <c r="C31" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="39" t="n">
+      <c r="A32" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="43" t="n">
         <v>0.02</v>
       </c>
-      <c r="C32" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>109</v>
+      <c r="C32" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>113</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="24" t="s">
-        <v>111</v>
+      <c r="A34" s="30" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="25" t="s">
-        <v>112</v>
+      <c r="A35" s="31" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="25" t="s">
-        <v>113</v>
+      <c r="A36" s="31" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="25" t="s">
-        <v>114</v>
+      <c r="A37" s="31" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="25"/>
+      <c r="A38" s="31"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24" t="s">
-        <v>115</v>
+      <c r="A39" s="30" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="25" t="s">
-        <v>116</v>
+      <c r="A40" s="31" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="25" t="s">
-        <v>117</v>
+      <c r="A41" s="31" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="25" t="s">
-        <v>118</v>
+      <c r="A42" s="31" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -6048,286 +6388,286 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="40" t="s">
-        <v>124</v>
+        <v>126</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>128</v>
+      <c r="A5" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>132</v>
+      <c r="A6" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="46" t="s">
+      <c r="A7" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="49" t="s">
         <v>135</v>
       </c>
+      <c r="D7" s="50" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>139</v>
+      <c r="A8" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>139</v>
+      <c r="A9" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>145</v>
+      <c r="A10" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>148</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>149</v>
+      <c r="A11" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="B12" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="45" t="s">
+      <c r="A12" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="D12" s="47" t="s">
-        <v>152</v>
+      <c r="C12" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41" t="s">
-        <v>153</v>
-      </c>
-      <c r="B13" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>155</v>
+      <c r="A13" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>159</v>
+      <c r="A14" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="B15" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="C15" s="45" t="s">
+      <c r="A15" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="D15" s="45" t="s">
-        <v>162</v>
+      <c r="C15" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="D16" s="52" t="s">
-        <v>166</v>
+      <c r="A16" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>169</v>
+      </c>
+      <c r="D16" s="56" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="53" t="s">
-        <v>167</v>
+      <c r="A18" s="57" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="54" t="s">
-        <v>168</v>
+      <c r="A19" s="58" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="55" t="s">
-        <v>169</v>
+      <c r="A20" s="59" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="55"/>
+      <c r="A21" s="59"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="56" t="s">
-        <v>170</v>
+      <c r="A22" s="60" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="55" t="s">
-        <v>171</v>
+      <c r="A23" s="59" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="55"/>
+      <c r="A24" s="59"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="57" t="s">
-        <v>172</v>
+      <c r="A25" s="61" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="55" t="s">
-        <v>173</v>
+      <c r="A26" s="59" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="55" t="s">
-        <v>174</v>
+      <c r="A27" s="59" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="55" t="s">
-        <v>175</v>
+      <c r="A28" s="59" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="55"/>
+      <c r="A29" s="59"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="55" t="s">
-        <v>176</v>
+      <c r="A30" s="59" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="55" t="s">
-        <v>177</v>
+      <c r="A31" s="59" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="55"/>
+      <c r="A32" s="59"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="53" t="s">
-        <v>178</v>
+      <c r="A33" s="57" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="55" t="s">
-        <v>179</v>
+      <c r="A34" s="59" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="55" t="s">
-        <v>180</v>
+      <c r="A35" s="59" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="55" t="s">
-        <v>181</v>
+      <c r="A36" s="59" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="55" t="s">
-        <v>182</v>
+      <c r="A37" s="59" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -6355,173 +6695,173 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="58" t="s">
-        <v>184</v>
-      </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
+      <c r="A3" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="41" t="s">
-        <v>187</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>189</v>
+      <c r="A6" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>192</v>
+      <c r="A7" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>195</v>
+      <c r="A8" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>198</v>
+      <c r="A9" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="41" t="s">
-        <v>199</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>201</v>
+      <c r="A10" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="53" t="s">
-        <v>202</v>
+      <c r="A12" s="57" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="55"/>
+      <c r="A13" s="59"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="59" t="s">
-        <v>203</v>
+      <c r="A14" s="63" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="55" t="s">
-        <v>204</v>
+      <c r="A15" s="59" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="55" t="s">
-        <v>205</v>
+      <c r="A16" s="59" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="55"/>
+      <c r="A17" s="59"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="59" t="s">
-        <v>206</v>
+      <c r="A18" s="63" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="55" t="s">
-        <v>207</v>
+      <c r="A19" s="59" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="55" t="s">
-        <v>208</v>
+      <c r="A20" s="59" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="55" t="s">
-        <v>209</v>
+      <c r="A21" s="59" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="55"/>
+      <c r="A22" s="59"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="59" t="s">
-        <v>210</v>
+      <c r="A23" s="63" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="55" t="s">
-        <v>211</v>
+      <c r="A24" s="59" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="55"/>
+      <c r="A25" s="59"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="53" t="s">
-        <v>212</v>
+      <c r="A26" s="57" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="59" t="s">
-        <v>213</v>
+      <c r="A27" s="63" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="59" t="s">
-        <v>214</v>
+      <c r="A28" s="63" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="59" t="s">
-        <v>215</v>
+      <c r="A29" s="63" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="59" t="s">
-        <v>216</v>
+      <c r="A30" s="63" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="55"/>
+      <c r="A31" s="59"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="60" t="s">
-        <v>217</v>
+      <c r="A32" s="64" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
